--- a/data/trans_orig/P41D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023</t>
+          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,62 +765,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5591</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,97 +1073,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>41,1%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3545</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,1%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4496</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>26,77%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4568</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1759,97 +1759,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1368</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3058</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>78,5%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>724</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3094</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3812</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3212</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1524,92 +1524,92 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2153</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2193</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>47,79%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
